--- a/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
@@ -627,7 +627,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -1497,9 +1497,8 @@
     <row r="25"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="L13:R13"/>

--- a/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,18 +78,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="22"/>
@@ -125,8 +113,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -146,11 +138,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,38 +178,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,13 +214,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -617,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -631,13 +612,12 @@
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,304 +628,232 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.13)</t>
+          <t>SR26 sustainability reporting (v0.14)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>End-2026 target status confirmation and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Target status assessment and definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+          <t>SR26 sustainability reporting request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>• Confirm target status for each row below (Column L). Refer to target status definitions to the right for guidance.
-• Provide commentary on progress towards each target (Column M or N)
-• Provide supporting documentation if required (Column O), including links to images
-• Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
+• Provide supporting information if required (Column N), including links to documents or images
+• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
-• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
+• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
 • Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided demonstrates that the Faculty/Portfolio has met or exceeded the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided indicates that the target has not been met, but there has been a significant improvement and performance is trending towards the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>Some action has been taken to address the target, but the data and information provided demonstrates that this has been insufficient to meet the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>No action has been taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="L8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Note: target status definitions are under review for 2027 reporting. 2026 ratings are for internal management reporting only.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="60" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>ABP – Faculty of Architecture, Building and Planning</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of how your faculty has embedded sustainability in teaching and learning. This could include innovative approaches (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment or learning resources) and sustainability-focused experiential or co-curricular learning (e.g. industry or community projects, fieldwork, internships, student challenges). Include links and approximate student participation where known.
 This question also covers indicator EE1(c). Melbourne Plus and the Wattle Fellowship will be collected separately – no need to report these.</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>4a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>The Faculty has continued to make substantial and discipline-wide progress in embedding sustainability into the curriculum in ways that extend well beyond baseline requirements, ensuring that students critically engage with both the beneficial and harmful impacts of the built environment on environmental and human systems.
 A central mechanism for this work in 2025 has been the forward planning and strategic renewal of all Master’s programs across the Faculty, led by Professor Dan Hill under the Designing Futures strategy. This process goes beyond incremental subject updates and instead focuses on holistic program-level reform, explicitly positioning sustainability as a core organising principle rather than an add-on topic.
@@ -959,108 +867,106 @@
 Together, these initiatives demonstrate a deliberate and sustained commitment to embedding sustainability deeply and coherently across the curriculum, ensuring that graduates across all disciplines develop a critical understanding of the environmental and human systems they shape through professional practice.</t>
         </is>
       </c>
-      <c r="K16" s="19" t="inlineStr"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Has your faculty piloted or trialled any approach in 2026 to understand or build students' confidence and capability to act on sustainability (sustainability self-efficacy)? If yes, briefly describe the approach, participating cohort, what was learned and next steps. If not, please respond 'none in 2026' – this is a new indicator and a nil response is useful.
 We are aware of the Sustainability Strengths Compass Living Lab project (CLLAP) and will collect it separately.</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr"/>
-      <c r="J17" s="19" t="inlineStr"/>
-      <c r="K17" s="19" t="inlineStr"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="21" t="n"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
 We will collect Campus Living Lab Accelerator Program (CLLAP) projects separately from CI&amp;S – please include other examples only.</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>Across 2025, the Faculty of Architecture, Building and Planning has significantly strengthened and formalised its Living Labs approach, building on progress reported at mid-year and embedding sustainability experimentation as a core mode of practice across teaching, research, and operations.
 A major development in the second half of 2025 was the establishment of the ABP Sustainability Grant. This new internal funding scheme provides up to $10,000 annually to catalyse staff-led, cross-disciplinary sustainability initiatives that operate as Living Labs within the Faculty. The scheme supports projects that use real faculty contexts—spaces, systems, practices, and communities—as testbeds for sustainability innovation, with strong encouragement for student involvement, particularly graduate researchers.
@@ -1074,60 +980,59 @@
 Together with the newly established ABP Sustainability Grant, the Interactive Campus Material and Carbon Atlas illustrates how the Faculty is operationalising Living Labs across scales—from grassroots initiatives to faculty-wide decision-support infrastructure.</t>
         </is>
       </c>
-      <c r="K18" s="19" t="inlineStr"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
-      <c r="P18" s="21" t="n"/>
-      <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="21" t="n"/>
+      <c r="K18" s="14" t="inlineStr"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="16" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>TR2(a)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
 We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from MRE – publication counts are not required.</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from MRE.</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J19" s="19" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>The Faculty continues to be a national and international leader in sustainability research across the built environment, supported by a diverse ecosystem of specialist research hubs, laboratories, and collaborative initiatives. Together, these centres span disciplinary and interdisciplinary research, linking fundamental inquiry with applied outcomes that inform practice, policy, and industry transformation.
 Sustainability-, climate-, and environment-focused research institutes and hubs within the Faculty include:
@@ -1148,64 +1053,63 @@
 As such, Beyond EPiC exemplifies the Faculty’s model of sustainability research impact: scientifically rigorous, trusted by government, used at scale, and capable of shaping policy, professional practice, and environmental outcomes simultaneously.</t>
         </is>
       </c>
-      <c r="K19" s="19" t="inlineStr">
+      <c r="K19" s="14" t="inlineStr">
         <is>
           <t>www.beyondepic.io</t>
         </is>
       </c>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
-      <c r="P19" s="21" t="n"/>
-      <c r="Q19" s="21" t="n"/>
-      <c r="R19" s="21" t="n"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="16" t="n"/>
+      <c r="O19" s="16" t="n"/>
+      <c r="P19" s="16" t="n"/>
+      <c r="Q19" s="16" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>TR2(d)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
 We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>The Faculty continues to be a national and international leader in sustainability research across the built environment, supported by a diverse ecosystem of specialist research hubs, laboratories, and collaborative initiatives. Together, these centres span disciplinary and interdisciplinary research, linking fundamental inquiry with applied outcomes that inform practice, policy, and industry transformation.
 Sustainability-, climate-, and environment-focused research institutes and hubs within the Faculty include:
@@ -1226,63 +1130,62 @@
 As such, Beyond EPiC exemplifies the Faculty’s model of sustainability research impact: scientifically rigorous, trusted by government, used at scale, and capable of shaping policy, professional practice, and environmental outcomes simultaneously.</t>
         </is>
       </c>
-      <c r="K20" s="19" t="inlineStr">
+      <c r="K20" s="14" t="inlineStr">
         <is>
           <t>www.beyondepic.io</t>
         </is>
       </c>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="21" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="16" t="n"/>
     </row>
     <row r="21" ht="150" customHeight="1">
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr">
         <is>
           <t>5c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>The Faculty has taken deliberate and strategic steps in 2025 to strengthen how sustainability considerations shape research practices and activities. This has focused on making sustainability explicit, visible, and rewarded within the Faculty’s research culture, while building the foundations for longer-term embedding across disciplines.
 A major development has been the introduction of formal recognition and incentive mechanisms that foreground sustainability in research excellence. The ABP Sustainability Award, embedded within the Faculty’s Engagement, Culture, Innovation, and Impact awards program, recognises academic and professional staff who demonstrate leadership in integrating sustainability into research practices. By celebrating approaches such as life cycle thinking, low-carbon methodologies, resource efficiency, and collaborative research models, the award signals that sustainability is a core dimension of research quality and impact within ABP.
@@ -1291,59 +1194,58 @@
 Together, these initiatives reflect a maturing research culture in which sustainability is increasingly normalised, recognised, and actively shaped through incentives, methods, and shared expectations. While this work will continue to evolve and scale, 2025 represents a clear step change in positioning sustainability as a defining feature of responsible research practice within the Faculty.</t>
         </is>
       </c>
-      <c r="K21" s="19" t="inlineStr"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="21" t="n"/>
-      <c r="P21" s="21" t="n"/>
-      <c r="Q21" s="21" t="n"/>
-      <c r="R21" s="21" t="n"/>
+      <c r="K21" s="14" t="inlineStr"/>
+      <c r="L21" s="16" t="n"/>
+      <c r="M21" s="16" t="n"/>
+      <c r="N21" s="16" t="n"/>
+      <c r="O21" s="16" t="n"/>
+      <c r="P21" s="16" t="n"/>
+      <c r="Q21" s="16" t="n"/>
     </row>
     <row r="22" ht="150" customHeight="1">
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr">
         <is>
           <t>6a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>In 2025, the Faculty has continued to deepen its engagement with sustainability through Indigenous-led and co-created learning, research, and partnerships, strengthening understanding of sustainability as a Country-centred, relational, and long-term responsibility rather than a purely technical or extractive concept.
 A major development is the award of an ARC Linkage Project: Co-designing Housing for First Nations Prosperity, which will commence in 2026. This project represents a significant example of sustainability research grounded in First Nations leadership, knowledge, and lived experience, operating at the intersection of architecture, housing policy, economics, and Indigenous wellbeing.
@@ -1354,60 +1256,59 @@
 Collectively, these initiatives demonstrate that the Faculty’s approach to sustainability is increasingly shaped through Indigenous-led knowledge systems, reciprocal learning, and co-creation, contributing to more just, culturally grounded, and enduring sustainability outcomes across education, research, and practice.</t>
         </is>
       </c>
-      <c r="K22" s="19" t="inlineStr"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
-      <c r="P22" s="21" t="n"/>
-      <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="21" t="n"/>
+      <c r="K22" s="14" t="inlineStr"/>
+      <c r="L22" s="16" t="n"/>
+      <c r="M22" s="16" t="n"/>
+      <c r="N22" s="16" t="n"/>
+      <c r="O22" s="16" t="n"/>
+      <c r="P22" s="16" t="n"/>
+      <c r="Q22" s="16" t="n"/>
     </row>
     <row r="23" ht="150" customHeight="1">
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
 Please note we will approach living labs funded through the Campus Living Lab Accelerator Program (CLLAP) separately.</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
         </is>
       </c>
-      <c r="H23" s="20" t="inlineStr">
+      <c r="H23" s="15" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>Across 2025, the Faculty of Architecture, Building and Planning has significantly strengthened and formalised its Living Labs approach, building on progress reported at mid-year and embedding sustainability experimentation as a core mode of practice across teaching, research, and operations.
 A major development in the second half of 2025 was the establishment of the ABP Sustainability Grant. This new internal funding scheme provides up to $10,000 annually to catalyse staff-led, cross-disciplinary sustainability initiatives that operate as Living Labs within the Faculty. The scheme supports projects that use real faculty contexts—spaces, systems, practices, and communities—as testbeds for sustainability innovation, with strong encouragement for student involvement, particularly graduate researchers.
@@ -1421,59 +1322,58 @@
 Together with the newly established ABP Sustainability Grant, the Interactive Campus Material and Carbon Atlas illustrates how the Faculty is operationalising Living Labs across scales—from grassroots initiatives to faculty-wide decision-support infrastructure.</t>
         </is>
       </c>
-      <c r="K23" s="19" t="inlineStr"/>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="21" t="n"/>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="21" t="n"/>
-      <c r="P23" s="21" t="n"/>
-      <c r="Q23" s="21" t="n"/>
-      <c r="R23" s="21" t="n"/>
+      <c r="K23" s="14" t="inlineStr"/>
+      <c r="L23" s="16" t="n"/>
+      <c r="M23" s="16" t="n"/>
+      <c r="N23" s="16" t="n"/>
+      <c r="O23" s="16" t="n"/>
+      <c r="P23" s="16" t="n"/>
+      <c r="Q23" s="16" t="n"/>
     </row>
     <row r="24" ht="150" customHeight="1">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="H24" s="15" t="inlineStr">
         <is>
           <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>In 2025, ABP continued to support sustainability-focused communities of practice that enable staff to learn from one another and embed sustainability across formal, non-formal, and informal learning contexts. These communities operate through a combination of structured forums, shared initiatives, and recognition mechanisms that make sustainability practice visible, valued, and transferable across the Faculty.
 Core to this ecosystem is the Faculty’s Climate Action Group, which continues to provide a cross-disciplinary forum for peer learning, curriculum coordination, and shared reflection on sustainability pedagogy and practice. The Group has supported sustained collaboration across academic and professional staff and has played a key role in aligning Faculty initiatives with University sustainability priorities.
@@ -1485,34 +1385,25 @@
 In this way, the Sustainability Award complements more formal communities of practice by creating a visible, Faculty-wide platform for knowledge sharing, inspiration, and peer learning. It supports sustainability not only as a technical or curricular concern, but as a shared professional and cultural endeavour.</t>
         </is>
       </c>
-      <c r="K24" s="19" t="inlineStr"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
-      <c r="P24" s="21" t="n"/>
-      <c r="Q24" s="21" t="n"/>
-      <c r="R24" s="21" t="n"/>
+      <c r="K24" s="14" t="inlineStr"/>
+      <c r="L24" s="16" t="n"/>
+      <c r="M24" s="16" t="n"/>
+      <c r="N24" s="16" t="n"/>
+      <c r="O24" s="16" t="n"/>
+      <c r="P24" s="16" t="n"/>
+      <c r="Q24" s="16" t="n"/>
     </row>
     <row r="25"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="9">
-    <mergeCell ref="M7:N7"/>
+  <mergeCells count="4">
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L16:L24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q16:Q24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="P16:P24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1559,7 +1450,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting</t>
+          <t>SR26 sustainability reporting</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1462,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
@@ -1584,77 +1475,77 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1705,90 +1596,90 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>ABP</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>1a(i)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Comment on progress to reduce air travel emissions in the faculty</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Faculty-level air travel data for 2025 indicates that the Faculty of Architecture, Building and Planning (ABP) has continued to reduce its contribution to University-wide air travel emissions, supporting progress toward the University’s carbon neutrality target.
 According to the 2025 Flights Dashboard, ABP recorded 375 tCO₂-e from air travel in 2025, representing approximately 2% of total University air travel emissions. This places ABP among the lowest-emitting faculties in absolute terms, despite the Faculty’s strong international research and engagement profile.
@@ -1804,37 +1695,37 @@
 While international travel remains a significant and sometimes necessary component of ABP’s research and engagement activities, the 2025 data indicates that the Faculty has achieved meaningful and sustained reductions in air travel emissions relative to historic levels. Further opportunities for reduction are being explored through internal discussions on travel justification, approval processes, and the strategic use of low-carbon alternatives, with a view to consolidating and extending these gains into 2026 and beyond.</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr"/>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/links/SI8xYFLga4?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;pbi_source=linkShare&amp;bookmarkGuid=499326eb-68f1-43e0-a3e6-0f252ee44ccb</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Please provide a case study of a living lab which operates within the faculty/portfolio, including a description of its activities and impact. 
 Please note we will approach living labs funded through the Campus Living Lab Accelerator program (CLLAP) separately report on their activities.</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>Across 2025, the Faculty of Architecture, Building and Planning has significantly strengthened and formalised its Living Labs approach, building on progress reported at mid-year and embedding sustainability experimentation as a core mode of practice across teaching, research, and operations.
 A major development in the second half of 2025 was the establishment of the ABP Sustainability Grant. This new internal funding scheme provides up to $10,000 annually to catalyse staff-led, cross-disciplinary sustainability initiatives that operate as Living Labs within the Faculty. The scheme supports projects that use real faculty contexts—spaces, systems, practices, and communities—as testbeds for sustainability innovation, with strong encouragement for student involvement, particularly graduate researchers.
@@ -1843,7 +1734,7 @@
 Collectively, these initiatives demonstrate that ABP is not only contributing to the University’s Living Labs agenda, but actively curating, resourcing, and governing Living Labs as a sustained and scalable approach to sustainability action.</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>A flagship example of the Faculty’s Living Labs approach in 2025 is the Interactive Campus Material and Carbon Atlas, which reached completion during the year. Funded through the Learning and Teaching Initiative (LTI), the project brought together academic staff, professional colleagues, and students to map and analyse the material stock and embodied carbon of selected University buildings.
 The Atlas has been developed as an interactive digital tool that enables users to explore building-level data, including construction materials, embodied carbon intensities, and potential opportunities for material reuse and circularity. Importantly, the project moves beyond retrospective analysis: the underlying framework enables forward projection of material requirements and carbon implications under different development and renewal scenarios.
@@ -1852,35 +1743,35 @@
 Together with the newly established ABP Sustainability Grant, the Interactive Campus Material and Carbon Atlas illustrates how the Faculty is operationalising Living Labs across scales—from grassroots initiatives to faculty-wide decision-support infrastructure.</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr"/>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>TR1(a), EN1(b)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>3a(i)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Please update data on sustainability-focused staff in the faculty/portfolio provided in the previous reporting period (additional staff/those who have left the University) (see Columns G [2024] and J [mid-2025])</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>In 2025, ABP continued to strengthen how sustainability is embedded across formal, non-formal, and informal learning and practice through distributed leadership and coordinated collaboration. Strategic oversight is provided through the Assistant Dean (Sustainability) role, alongside active cross-disciplinary networks (including the Climate Action Group) that support curriculum integration, peer learning, and shared resourcing across departments.
 A key step-change in the second half of 2025 was the establishment of the ABP Sustainability Grant, which has also functioned as a practical mechanism for identifying, mobilising, and connecting sustainability-focused staff across the Faculty. The scheme requires project teams to include both academic and professional staff, with strong encouragement for student involvement. This requirement has actively enabled collaboration between staff groups that do not typically co-lead initiatives together, supporting mutual learning and the transfer of sustainability knowledge into operational and teaching contexts.
@@ -1888,7 +1779,7 @@
 Regardless of the final funding outcomes, the Faculty is committed to supporting high-quality proposals and ensuring that strong ideas emerging through the scheme are enabled to progress—either through the grant itself or through alternative pathways—so that sustainability leadership and learning continues to be shared and scaled across ABP.</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>As supporting evidence of increased sustainability-focused participation and cross-role collaboration in 2025, the Faculty established the ABP Sustainability Grant, which requires teams to include at least one academic and one professional staff member and encourages student participation. The inaugural round drew multiple applications across diverse roles and disciplines, including proposals focused on:
 &gt; establishing a circular timber pathway through salvage, low-energy processing, and reuse integrated with teaching and workshop operations; and
@@ -1896,31 +1787,31 @@
 These proposals demonstrate both the breadth of sustainability-focused staff across ABP and the Faculty’s active approach to enabling staff to support and learn from each other in embedding sustainability into practice and learning.</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr"/>
-      <c r="I9" s="19" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>3a(ii)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Please list sustainability-focused knowledge sharing activities or communities of practice active in the faculty/portfolio in 2025, and provide a short case study of one of these.</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>In 2025, ABP continued to support sustainability-focused communities of practice that enable staff to learn from one another and embed sustainability across formal, non-formal, and informal learning contexts. These communities operate through a combination of structured forums, shared initiatives, and recognition mechanisms that make sustainability practice visible, valued, and transferable across the Faculty.
 Core to this ecosystem is the Faculty’s Climate Action Group, which continues to provide a cross-disciplinary forum for peer learning, curriculum coordination, and shared reflection on sustainability pedagogy and practice. The Group has supported sustained collaboration across academic and professional staff and has played a key role in aligning Faculty initiatives with University sustainability priorities.
@@ -1928,7 +1819,7 @@
 Complementing these collaborative forums, the Faculty introduced the ABP Sustainability Award as a mechanism for amplifying and connecting sustainability practice across teaching, research, operations, and Faculty culture. Together, these initiatives demonstrate a mature and multi-layered approach to building sustainability-focused communities of practice—combining regular peer engagement, high-impact knowledge exchange, and recognition of exemplary work to support ongoing learning and leadership in sustainability.</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Introduced in 2025, the ABP Sustainability Award functions as a Faculty-wide community-of-practice mechanism by recognising, showcasing, and disseminating exemplary sustainability initiatives led by academic and professional staff. Rather than operating solely as an individual award, the scheme is designed to surface transferable practices and create shared reference points for sustainability leadership across ABP.
 The Award recognises excellence across a broad set of criteria, including innovation and leadership, collaboration and engagement, measurable environmental outcomes, integration of sustainability into teaching and learning, influence on policy and professional practice, and contributions to a culture of sustainability within the Faculty. Eligible initiatives span teaching, research, operations, and cultural change, reflecting the diverse ways sustainability is embedded across ABP.
@@ -1936,36 +1827,36 @@
 In this way, the Sustainability Award complements more formal communities of practice by creating a visible, Faculty-wide platform for knowledge sharing, inspiration, and peer learning. It supports sustainability not only as a technical or curricular concern, but as a shared professional and cultural endeavour.</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>3d(ii)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Have any staff participated in sustainability-focused professional development in 2025? If yes, what kinds of activities have staff participated in and how are these learnings being applied in the faculty/portfolio?
 Please note, there is no need to include data on participation in Green Impact ('Green teams'), as this is reported on centrally.</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>In 2025, ABP supported the development of staff sustainability capability through a combination of non-formal, practice-based learning and peer-led knowledge exchange. While participation in centrally delivered, formal professional development was limited due to broader institutional transitions, the Faculty remained actively engaged in alternative learning pathways that supported both general and role-specific sustainability skills.
 As reported at mid-year, several established executive and professional education offerings—including the Embodied Carbon Masterclass previously delivered in partnership with MSPACE—were paused in 2025 as delivery models were reviewed. In response, the Faculty placed greater emphasis on applied, embedded learning opportunities linked directly to teaching, research, and professional practice.
@@ -1976,32 +1867,32 @@
 These activities enabled staff to develop and apply sustainability skills directly relevant to their roles, while also fostering peer learning across disciplines and professional functions. While formal professional development participation remained stable in 2025, these applied learning initiatives ensured continued capability building during a period of transition, with significant expansion anticipated through the Faculty’s refreshed executive and professional education model from 2027.</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr"/>
-      <c r="H11" s="19" t="inlineStr"/>
-      <c r="I11" s="19" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="160" customHeight="1">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>4a(ii)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Please describe any efforts within your faculty to embed sustainability in the curriculum in line with this target.</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>The Faculty has continued to make substantial and discipline-wide progress in embedding sustainability into the curriculum in ways that extend well beyond baseline requirements, ensuring that students critically engage with both the beneficial and harmful impacts of the built environment on environmental and human systems.
 A central mechanism for this work in 2025 has been the forward planning and strategic renewal of all Master’s programs across the Faculty, led by Professor Dan Hill under the Designing Futures strategy. This process goes beyond incremental subject updates and instead focuses on holistic program-level reform, explicitly positioning sustainability as a core organising principle rather than an add-on topic.
@@ -2015,36 +1906,36 @@
 Together, these initiatives demonstrate a deliberate and sustained commitment to embedding sustainability deeply and coherently across the curriculum, ensuring that graduates across all disciplines develop a critical understanding of the environmental and human systems they shape through professional practice.</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr"/>
-      <c r="H12" s="19" t="inlineStr"/>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="160" customHeight="1">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>4b(i)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead and succeed in the careers, communities and industries of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Is there any way to measure graduate outcomes related to sustainability in your faculty? If so, please describe.</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>The Faculty recognises the importance of understanding how graduates develop the capabilities required to shape, lead and succeed in sustainable societies. At present, however, there is no single quantitative metric that adequately captures graduate sustainability capability across the breadth and depth of the Faculty’s programs.
 While subject completions with sustainability-related content are sometimes used as a proxy indicator, the Faculty continues to view this as a limited and potentially misleading measure. Sustainability capability at ABP is increasingly developed through integrated curricula, studio-based learning, project work, and practice-oriented engagement, where sustainability is embedded in learning outcomes, assessment criteria, and decision-making processes rather than delivered as discrete content that can be easily counted.
@@ -2056,36 +1947,36 @@
 The Faculty acknowledges that these outcomes are not yet systematically captured through a formal reporting framework. Over time, ABP intends to develop more meaningful indicators of graduate sustainability capability, potentially combining curriculum mapping, assessment alignment, graduate destination insights, and qualitative exemplars of student work. This will support more robust reporting in future Sustainability Plan refresh cycles, while ensuring that measurement aligns with the complexity and integrated nature of sustainability education within the built environment disciplines.</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr"/>
-      <c r="H13" s="19" t="inlineStr"/>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="160" customHeight="1">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>5b(i)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Please update data on sustainability-, climate- or environment-focused research institutes, and provide a case study of their key research impacts in 2025.</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>The Faculty continues to be a national and international leader in sustainability research across the built environment, supported by a diverse ecosystem of specialist research hubs, laboratories, and collaborative initiatives. Together, these centres span disciplinary and interdisciplinary research, linking fundamental inquiry with applied outcomes that inform practice, policy, and industry transformation.
 Sustainability-, climate-, and environment-focused research institutes and hubs within the Faculty include:
@@ -2099,7 +1990,7 @@
 These research hubs collectively contribute to advancing knowledge across design, planning, construction, and policy, while also creating pathways for translation into real-world impact.</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>A flagship example of the Faculty’s research impact in 2025 is Beyond EPiC, a research-led spin-off emerging from long-standing work within the Faculty on life cycle assessment (LCA), embodied carbon, and environmental performance of the built environment.
 Beyond EPiC provides a clear example of how the Faculty’s sustainability research translates into action and impact at scale. Emerging directly from decades of peer-reviewed research at the University of Melbourne, Beyond EPiC develops environmental data, digital tools, and applied insights that help architects, engineers, planners, developers, and policymakers make evidence-based decisions across the built environment.
@@ -2110,39 +2001,39 @@
 As such, Beyond EPiC exemplifies the Faculty’s model of sustainability research impact: scientifically rigorous, trusted by government, used at scale, and capable of shaping policy, professional practice, and environmental outcomes simultaneously.</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>www.beyondepic.io</t>
         </is>
       </c>
-      <c r="I14" s="19" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>TR2(a), TR2(d)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="160" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>5c(ii)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Researchers make considered decisions on the sustainability impact of their research practices and activities</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Are there any efforts within the faculty to make research practices more sustainable? If so, please describe these activities</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>The Faculty has taken deliberate and strategic steps in 2025 to strengthen how sustainability considerations shape research practices and activities. This has focused on making sustainability explicit, visible, and rewarded within the Faculty’s research culture, while building the foundations for longer-term embedding across disciplines.
 A major development has been the introduction of formal recognition and incentive mechanisms that foreground sustainability in research excellence. The ABP Sustainability Award, embedded within the Faculty’s Engagement, Culture, Innovation, and Impact awards program, recognises academic and professional staff who demonstrate leadership in integrating sustainability into research practices. By celebrating approaches such as life cycle thinking, low-carbon methodologies, resource efficiency, and collaborative research models, the award signals that sustainability is a core dimension of research quality and impact within ABP.
@@ -2151,36 +2042,36 @@
 Together, these initiatives reflect a maturing research culture in which sustainability is increasingly normalised, recognised, and actively shaped through incentives, methods, and shared expectations. While this work will continue to evolve and scale, 2025 represents a clear step change in positioning sustainability as a defining feature of responsible research practice within the Faculty.</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr"/>
-      <c r="H15" s="19" t="inlineStr"/>
-      <c r="I15" s="19" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>TR3(a), TR3(b)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="160" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Please provide a case study on activities in the faculty (related to education, research or partnerships) which operate at the nexus between Indigenous knowledges and the western concept of 'sustainability'.</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>In 2025, the Faculty has continued to deepen its engagement with sustainability through Indigenous-led and co-created learning, research, and partnerships, strengthening understanding of sustainability as a Country-centred, relational, and long-term responsibility rather than a purely technical or extractive concept.
 A major development is the award of an ARC Linkage Project: Co-designing Housing for First Nations Prosperity, which will commence in 2026. This project represents a significant example of sustainability research grounded in First Nations leadership, knowledge, and lived experience, operating at the intersection of architecture, housing policy, economics, and Indigenous wellbeing.
@@ -2191,9 +2082,9 @@
 Collectively, these initiatives demonstrate that the Faculty’s approach to sustainability is increasingly shaped through Indigenous-led knowledge systems, reciprocal learning, and co-creation, contributing to more just, culturally grounded, and enduring sustainability outcomes across education, research, and practice.</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr"/>
-      <c r="H16" s="19" t="inlineStr"/>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr"/>
+      <c r="H16" s="14" t="inlineStr"/>
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
@@ -2216,13 +2107,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>End 2026 target status</t>
+          <t>(not used – no target status rating in 2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -2238,21 +2129,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
         </is>
       </c>
     </row>
@@ -2277,24 +2153,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -2310,24 +2170,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -2343,47 +2187,15 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
@@ -2391,11 +2203,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>

--- a/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
@@ -20,21 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="00002060"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -178,61 +170,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,32 +610,22 @@
     <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting (v0.16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -661,199 +641,202 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="60" customHeight="1"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>ABP – Faculty of Architecture, Building and Planning</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="7" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+    <row r="15" ht="81" customHeight="1">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+    <row r="16" ht="320" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of how your faculty has embedded sustainability in teaching and learning. This could include innovative approaches (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment or learning resources) and sustainability-focused experiential or co-curricular learning (e.g. industry or community projects, fieldwork, internships, student challenges). Include links and approximate student participation where known.
 This question also covers indicator EE1(c). Melbourne Plus and the Wattle Fellowship will be collected separately – no need to report these.</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>4a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>The Faculty has continued to make substantial and discipline-wide progress in embedding sustainability into the curriculum in ways that extend well beyond baseline requirements, ensuring that students critically engage with both the beneficial and harmful impacts of the built environment on environmental and human systems.
 A central mechanism for this work in 2025 has been the forward planning and strategic renewal of all Master’s programs across the Faculty, led by Professor Dan Hill under the Designing Futures strategy. This process goes beyond incremental subject updates and instead focuses on holistic program-level reform, explicitly positioning sustainability as a core organising principle rather than an add-on topic.
@@ -867,106 +850,106 @@
 Together, these initiatives demonstrate a deliberate and sustained commitment to embedding sustainability deeply and coherently across the curriculum, ensuring that graduates across all disciplines develop a critical understanding of the environmental and human systems they shape through professional practice.</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="188" customHeight="1">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Has your faculty piloted or trialled any approach in 2026 to understand or build students' confidence and capability to act on sustainability (sustainability self-efficacy)? If yes, briefly describe the approach, participating cohort, what was learned and next steps. If not, please respond 'none in 2026' – this is a new indicator and a nil response is useful.
 We are aware of the Sustainability Strengths Compass Living Lab project (CLLAP) and will collect it separately.</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="14" t="inlineStr"/>
-      <c r="K17" s="14" t="inlineStr"/>
-      <c r="L17" s="16" t="n"/>
-      <c r="M17" s="16" t="n"/>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="16" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="16" t="n"/>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr"/>
+      <c r="J17" s="12" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="14" t="n"/>
+      <c r="Q17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="303" customHeight="1">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
 We will collect Campus Living Lab Accelerator Program (CLLAP) projects separately from CI&amp;S – please include other examples only.</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>Across 2025, the Faculty of Architecture, Building and Planning has significantly strengthened and formalised its Living Labs approach, building on progress reported at mid-year and embedding sustainability experimentation as a core mode of practice across teaching, research, and operations.
 A major development in the second half of 2025 was the establishment of the ABP Sustainability Grant. This new internal funding scheme provides up to $10,000 annually to catalyse staff-led, cross-disciplinary sustainability initiatives that operate as Living Labs within the Faculty. The scheme supports projects that use real faculty contexts—spaces, systems, practices, and communities—as testbeds for sustainability innovation, with strong encouragement for student involvement, particularly graduate researchers.
@@ -980,59 +963,59 @@
 Together with the newly established ABP Sustainability Grant, the Interactive Campus Material and Carbon Atlas illustrates how the Faculty is operationalising Living Labs across scales—from grassroots initiatives to faculty-wide decision-support infrastructure.</t>
         </is>
       </c>
-      <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="16" t="n"/>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="16" t="n"/>
-    </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="K18" s="12" t="inlineStr"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="286" customHeight="1">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>TR2(a)</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
 We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from MRE – publication counts are not required.</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from MRE.</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>The Faculty continues to be a national and international leader in sustainability research across the built environment, supported by a diverse ecosystem of specialist research hubs, laboratories, and collaborative initiatives. Together, these centres span disciplinary and interdisciplinary research, linking fundamental inquiry with applied outcomes that inform practice, policy, and industry transformation.
 Sustainability-, climate-, and environment-focused research institutes and hubs within the Faculty include:
@@ -1053,63 +1036,63 @@
 As such, Beyond EPiC exemplifies the Faculty’s model of sustainability research impact: scientifically rigorous, trusted by government, used at scale, and capable of shaping policy, professional practice, and environmental outcomes simultaneously.</t>
         </is>
       </c>
-      <c r="K19" s="14" t="inlineStr">
+      <c r="K19" s="12" t="inlineStr">
         <is>
           <t>www.beyondepic.io</t>
         </is>
       </c>
-      <c r="L19" s="16" t="n"/>
-      <c r="M19" s="16" t="n"/>
-      <c r="N19" s="16" t="n"/>
-      <c r="O19" s="16" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="16" t="n"/>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="B20" s="12" t="inlineStr">
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="14" t="n"/>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="14" t="n"/>
+      <c r="Q19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="270" customHeight="1">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>TR2(d)</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
 We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>The Faculty continues to be a national and international leader in sustainability research across the built environment, supported by a diverse ecosystem of specialist research hubs, laboratories, and collaborative initiatives. Together, these centres span disciplinary and interdisciplinary research, linking fundamental inquiry with applied outcomes that inform practice, policy, and industry transformation.
 Sustainability-, climate-, and environment-focused research institutes and hubs within the Faculty include:
@@ -1130,62 +1113,62 @@
 As such, Beyond EPiC exemplifies the Faculty’s model of sustainability research impact: scientifically rigorous, trusted by government, used at scale, and capable of shaping policy, professional practice, and environmental outcomes simultaneously.</t>
         </is>
       </c>
-      <c r="K20" s="14" t="inlineStr">
+      <c r="K20" s="12" t="inlineStr">
         <is>
           <t>www.beyondepic.io</t>
         </is>
       </c>
-      <c r="L20" s="16" t="n"/>
-      <c r="M20" s="16" t="n"/>
-      <c r="N20" s="16" t="n"/>
-      <c r="O20" s="16" t="n"/>
-      <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="16" t="n"/>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="B21" s="12" t="inlineStr">
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="14" t="n"/>
+      <c r="Q20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="220" customHeight="1">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>5c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>The Faculty has taken deliberate and strategic steps in 2025 to strengthen how sustainability considerations shape research practices and activities. This has focused on making sustainability explicit, visible, and rewarded within the Faculty’s research culture, while building the foundations for longer-term embedding across disciplines.
 A major development has been the introduction of formal recognition and incentive mechanisms that foreground sustainability in research excellence. The ABP Sustainability Award, embedded within the Faculty’s Engagement, Culture, Innovation, and Impact awards program, recognises academic and professional staff who demonstrate leadership in integrating sustainability into research practices. By celebrating approaches such as life cycle thinking, low-carbon methodologies, resource efficiency, and collaborative research models, the award signals that sustainability is a core dimension of research quality and impact within ABP.
@@ -1194,58 +1177,58 @@
 Together, these initiatives reflect a maturing research culture in which sustainability is increasingly normalised, recognised, and actively shaped through incentives, methods, and shared expectations. While this work will continue to evolve and scale, 2025 represents a clear step change in positioning sustainability as a defining feature of responsible research practice within the Faculty.</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr"/>
-      <c r="L21" s="16" t="n"/>
-      <c r="M21" s="16" t="n"/>
-      <c r="N21" s="16" t="n"/>
-      <c r="O21" s="16" t="n"/>
-      <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="16" t="n"/>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="B22" s="12" t="inlineStr">
+      <c r="K21" s="12" t="inlineStr"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
+      <c r="N21" s="14" t="n"/>
+      <c r="O21" s="14" t="n"/>
+      <c r="P21" s="14" t="n"/>
+      <c r="Q21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="220" customHeight="1">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H22" s="15" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>6a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>In 2025, the Faculty has continued to deepen its engagement with sustainability through Indigenous-led and co-created learning, research, and partnerships, strengthening understanding of sustainability as a Country-centred, relational, and long-term responsibility rather than a purely technical or extractive concept.
 A major development is the award of an ARC Linkage Project: Co-designing Housing for First Nations Prosperity, which will commence in 2026. This project represents a significant example of sustainability research grounded in First Nations leadership, knowledge, and lived experience, operating at the intersection of architecture, housing policy, economics, and Indigenous wellbeing.
@@ -1256,59 +1239,59 @@
 Collectively, these initiatives demonstrate that the Faculty’s approach to sustainability is increasingly shaped through Indigenous-led knowledge systems, reciprocal learning, and co-creation, contributing to more just, culturally grounded, and enduring sustainability outcomes across education, research, and practice.</t>
         </is>
       </c>
-      <c r="K22" s="14" t="inlineStr"/>
-      <c r="L22" s="16" t="n"/>
-      <c r="M22" s="16" t="n"/>
-      <c r="N22" s="16" t="n"/>
-      <c r="O22" s="16" t="n"/>
-      <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="16" t="n"/>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="B23" s="12" t="inlineStr">
+      <c r="K22" s="12" t="inlineStr"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="14" t="n"/>
+      <c r="O22" s="14" t="n"/>
+      <c r="P22" s="14" t="n"/>
+      <c r="Q22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="254" customHeight="1">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
 Please note we will approach living labs funded through the Campus Living Lab Accelerator Program (CLLAP) separately.</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
         </is>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>Across 2025, the Faculty of Architecture, Building and Planning has significantly strengthened and formalised its Living Labs approach, building on progress reported at mid-year and embedding sustainability experimentation as a core mode of practice across teaching, research, and operations.
 A major development in the second half of 2025 was the establishment of the ABP Sustainability Grant. This new internal funding scheme provides up to $10,000 annually to catalyse staff-led, cross-disciplinary sustainability initiatives that operate as Living Labs within the Faculty. The scheme supports projects that use real faculty contexts—spaces, systems, practices, and communities—as testbeds for sustainability innovation, with strong encouragement for student involvement, particularly graduate researchers.
@@ -1322,58 +1305,58 @@
 Together with the newly established ABP Sustainability Grant, the Interactive Campus Material and Carbon Atlas illustrates how the Faculty is operationalising Living Labs across scales—from grassroots initiatives to faculty-wide decision-support infrastructure.</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr"/>
-      <c r="L23" s="16" t="n"/>
-      <c r="M23" s="16" t="n"/>
-      <c r="N23" s="16" t="n"/>
-      <c r="O23" s="16" t="n"/>
-      <c r="P23" s="16" t="n"/>
-      <c r="Q23" s="16" t="n"/>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="B24" s="12" t="inlineStr">
+      <c r="K23" s="12" t="inlineStr"/>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="14" t="n"/>
+      <c r="N23" s="14" t="n"/>
+      <c r="O23" s="14" t="n"/>
+      <c r="P23" s="14" t="n"/>
+      <c r="Q23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="188" customHeight="1">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>In 2025, ABP continued to support sustainability-focused communities of practice that enable staff to learn from one another and embed sustainability across formal, non-formal, and informal learning contexts. These communities operate through a combination of structured forums, shared initiatives, and recognition mechanisms that make sustainability practice visible, valued, and transferable across the Faculty.
 Core to this ecosystem is the Faculty’s Climate Action Group, which continues to provide a cross-disciplinary forum for peer learning, curriculum coordination, and shared reflection on sustainability pedagogy and practice. The Group has supported sustained collaboration across academic and professional staff and has played a key role in aligning Faculty initiatives with University sustainability priorities.
@@ -1385,13 +1368,13 @@
 In this way, the Sustainability Award complements more formal communities of practice by creating a visible, Faculty-wide platform for knowledge sharing, inspiration, and peer learning. It supports sustainability not only as a technical or curricular concern, but as a shared professional and cultural endeavour.</t>
         </is>
       </c>
-      <c r="K24" s="14" t="inlineStr"/>
-      <c r="L24" s="16" t="n"/>
-      <c r="M24" s="16" t="n"/>
-      <c r="N24" s="16" t="n"/>
-      <c r="O24" s="16" t="n"/>
-      <c r="P24" s="16" t="n"/>
-      <c r="Q24" s="16" t="n"/>
+      <c r="K24" s="12" t="inlineStr"/>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
+      <c r="N24" s="14" t="n"/>
+      <c r="O24" s="14" t="n"/>
+      <c r="P24" s="14" t="n"/>
+      <c r="Q24" s="14" t="n"/>
     </row>
     <row r="25"/>
   </sheetData>
@@ -1442,110 +1425,102 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="17" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1576,110 +1551,99 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2025 target status assessment and reporting (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Your SR25 responses – Faculty of Architecture, Building and Planning</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="22" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>ABP</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+    <row r="7" ht="409" customHeight="1">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>1a(i)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Comment on progress to reduce air travel emissions in the faculty</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Faculty-level air travel data for 2025 indicates that the Faculty of Architecture, Building and Planning (ABP) has continued to reduce its contribution to University-wide air travel emissions, supporting progress toward the University’s carbon neutrality target.
 According to the 2025 Flights Dashboard, ABP recorded 375 tCO₂-e from air travel in 2025, representing approximately 2% of total University air travel emissions. This places ABP among the lowest-emitting faculties in absolute terms, despite the Faculty’s strong international research and engagement profile.
@@ -1695,37 +1659,37 @@
 While international travel remains a significant and sometimes necessary component of ABP’s research and engagement activities, the 2025 data indicates that the Faculty has achieved meaningful and sustained reductions in air travel emissions relative to historic levels. Further opportunities for reduction are being explored through internal discussions on travel justification, approval processes, and the strategic use of low-carbon alternatives, with a view to consolidating and extending these gains into 2026 and beyond.</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/links/SI8xYFLga4?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;pbi_source=linkShare&amp;bookmarkGuid=499326eb-68f1-43e0-a3e6-0f252ee44ccb</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="409" customHeight="1">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Please provide a case study of a living lab which operates within the faculty/portfolio, including a description of its activities and impact. 
 Please note we will approach living labs funded through the Campus Living Lab Accelerator program (CLLAP) separately report on their activities.</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Across 2025, the Faculty of Architecture, Building and Planning has significantly strengthened and formalised its Living Labs approach, building on progress reported at mid-year and embedding sustainability experimentation as a core mode of practice across teaching, research, and operations.
 A major development in the second half of 2025 was the establishment of the ABP Sustainability Grant. This new internal funding scheme provides up to $10,000 annually to catalyse staff-led, cross-disciplinary sustainability initiatives that operate as Living Labs within the Faculty. The scheme supports projects that use real faculty contexts—spaces, systems, practices, and communities—as testbeds for sustainability innovation, with strong encouragement for student involvement, particularly graduate researchers.
@@ -1734,7 +1698,7 @@
 Collectively, these initiatives demonstrate that ABP is not only contributing to the University’s Living Labs agenda, but actively curating, resourcing, and governing Living Labs as a sustained and scalable approach to sustainability action.</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>A flagship example of the Faculty’s Living Labs approach in 2025 is the Interactive Campus Material and Carbon Atlas, which reached completion during the year. Funded through the Learning and Teaching Initiative (LTI), the project brought together academic staff, professional colleagues, and students to map and analyse the material stock and embodied carbon of selected University buildings.
 The Atlas has been developed as an interactive digital tool that enables users to explore building-level data, including construction materials, embodied carbon intensities, and potential opportunities for material reuse and circularity. Importantly, the project moves beyond retrospective analysis: the underlying framework enables forward projection of material requirements and carbon implications under different development and renewal scenarios.
@@ -1743,35 +1707,35 @@
 Together with the newly established ABP Sustainability Grant, the Interactive Campus Material and Carbon Atlas illustrates how the Faculty is operationalising Living Labs across scales—from grassroots initiatives to faculty-wide decision-support infrastructure.</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr"/>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>TR1(a), EN1(b)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="12" t="inlineStr">
+    <row r="9" ht="409" customHeight="1">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>3a(i)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Please update data on sustainability-focused staff in the faculty/portfolio provided in the previous reporting period (additional staff/those who have left the University) (see Columns G [2024] and J [mid-2025])</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>In 2025, ABP continued to strengthen how sustainability is embedded across formal, non-formal, and informal learning and practice through distributed leadership and coordinated collaboration. Strategic oversight is provided through the Assistant Dean (Sustainability) role, alongside active cross-disciplinary networks (including the Climate Action Group) that support curriculum integration, peer learning, and shared resourcing across departments.
 A key step-change in the second half of 2025 was the establishment of the ABP Sustainability Grant, which has also functioned as a practical mechanism for identifying, mobilising, and connecting sustainability-focused staff across the Faculty. The scheme requires project teams to include both academic and professional staff, with strong encouragement for student involvement. This requirement has actively enabled collaboration between staff groups that do not typically co-lead initiatives together, supporting mutual learning and the transfer of sustainability knowledge into operational and teaching contexts.
@@ -1779,7 +1743,7 @@
 Regardless of the final funding outcomes, the Faculty is committed to supporting high-quality proposals and ensuring that strong ideas emerging through the scheme are enabled to progress—either through the grant itself or through alternative pathways—so that sustainability leadership and learning continues to be shared and scaled across ABP.</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>As supporting evidence of increased sustainability-focused participation and cross-role collaboration in 2025, the Faculty established the ABP Sustainability Grant, which requires teams to include at least one academic and one professional staff member and encourages student participation. The inaugural round drew multiple applications across diverse roles and disciplines, including proposals focused on:
 &gt; establishing a circular timber pathway through salvage, low-energy processing, and reuse integrated with teaching and workshop operations; and
@@ -1787,31 +1751,31 @@
 These proposals demonstrate both the breadth of sustainability-focused staff across ABP and the Faculty’s active approach to enabling staff to support and learn from each other in embedding sustainability into practice and learning.</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr"/>
-      <c r="I9" s="14" t="inlineStr"/>
-    </row>
-    <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10" ht="409" customHeight="1">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>3a(ii)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Please list sustainability-focused knowledge sharing activities or communities of practice active in the faculty/portfolio in 2025, and provide a short case study of one of these.</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>In 2025, ABP continued to support sustainability-focused communities of practice that enable staff to learn from one another and embed sustainability across formal, non-formal, and informal learning contexts. These communities operate through a combination of structured forums, shared initiatives, and recognition mechanisms that make sustainability practice visible, valued, and transferable across the Faculty.
 Core to this ecosystem is the Faculty’s Climate Action Group, which continues to provide a cross-disciplinary forum for peer learning, curriculum coordination, and shared reflection on sustainability pedagogy and practice. The Group has supported sustained collaboration across academic and professional staff and has played a key role in aligning Faculty initiatives with University sustainability priorities.
@@ -1819,7 +1783,7 @@
 Complementing these collaborative forums, the Faculty introduced the ABP Sustainability Award as a mechanism for amplifying and connecting sustainability practice across teaching, research, operations, and Faculty culture. Together, these initiatives demonstrate a mature and multi-layered approach to building sustainability-focused communities of practice—combining regular peer engagement, high-impact knowledge exchange, and recognition of exemplary work to support ongoing learning and leadership in sustainability.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Introduced in 2025, the ABP Sustainability Award functions as a Faculty-wide community-of-practice mechanism by recognising, showcasing, and disseminating exemplary sustainability initiatives led by academic and professional staff. Rather than operating solely as an individual award, the scheme is designed to surface transferable practices and create shared reference points for sustainability leadership across ABP.
 The Award recognises excellence across a broad set of criteria, including innovation and leadership, collaboration and engagement, measurable environmental outcomes, integration of sustainability into teaching and learning, influence on policy and professional practice, and contributions to a culture of sustainability within the Faculty. Eligible initiatives span teaching, research, operations, and cultural change, reflecting the diverse ways sustainability is embedded across ABP.
@@ -1827,36 +1791,36 @@
 In this way, the Sustainability Award complements more formal communities of practice by creating a visible, Faculty-wide platform for knowledge sharing, inspiration, and peer learning. It supports sustainability not only as a technical or curricular concern, but as a shared professional and cultural endeavour.</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr"/>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="12" t="inlineStr">
+    <row r="11" ht="409" customHeight="1">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>3d(ii)</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Have any staff participated in sustainability-focused professional development in 2025? If yes, what kinds of activities have staff participated in and how are these learnings being applied in the faculty/portfolio?
 Please note, there is no need to include data on participation in Green Impact ('Green teams'), as this is reported on centrally.</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>In 2025, ABP supported the development of staff sustainability capability through a combination of non-formal, practice-based learning and peer-led knowledge exchange. While participation in centrally delivered, formal professional development was limited due to broader institutional transitions, the Faculty remained actively engaged in alternative learning pathways that supported both general and role-specific sustainability skills.
 As reported at mid-year, several established executive and professional education offerings—including the Embodied Carbon Masterclass previously delivered in partnership with MSPACE—were paused in 2025 as delivery models were reviewed. In response, the Faculty placed greater emphasis on applied, embedded learning opportunities linked directly to teaching, research, and professional practice.
@@ -1867,32 +1831,32 @@
 These activities enabled staff to develop and apply sustainability skills directly relevant to their roles, while also fostering peer learning across disciplines and professional functions. While formal professional development participation remained stable in 2025, these applied learning initiatives ensured continued capability building during a period of transition, with significant expansion anticipated through the Faculty’s refreshed executive and professional education model from 2027.</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr"/>
-      <c r="H11" s="14" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12" ht="160" customHeight="1">
-      <c r="B12" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr"/>
+      <c r="H11" s="12" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12" ht="409" customHeight="1">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>4a(ii)</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Please describe any efforts within your faculty to embed sustainability in the curriculum in line with this target.</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>The Faculty has continued to make substantial and discipline-wide progress in embedding sustainability into the curriculum in ways that extend well beyond baseline requirements, ensuring that students critically engage with both the beneficial and harmful impacts of the built environment on environmental and human systems.
 A central mechanism for this work in 2025 has been the forward planning and strategic renewal of all Master’s programs across the Faculty, led by Professor Dan Hill under the Designing Futures strategy. This process goes beyond incremental subject updates and instead focuses on holistic program-level reform, explicitly positioning sustainability as a core organising principle rather than an add-on topic.
@@ -1906,36 +1870,36 @@
 Together, these initiatives demonstrate a deliberate and sustained commitment to embedding sustainability deeply and coherently across the curriculum, ensuring that graduates across all disciplines develop a critical understanding of the environmental and human systems they shape through professional practice.</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr"/>
-      <c r="H12" s="14" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr"/>
+      <c r="H12" s="12" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="160" customHeight="1">
-      <c r="B13" s="12" t="inlineStr">
+    <row r="13" ht="409" customHeight="1">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>4b(i)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead and succeed in the careers, communities and industries of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Is there any way to measure graduate outcomes related to sustainability in your faculty? If so, please describe.</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>The Faculty recognises the importance of understanding how graduates develop the capabilities required to shape, lead and succeed in sustainable societies. At present, however, there is no single quantitative metric that adequately captures graduate sustainability capability across the breadth and depth of the Faculty’s programs.
 While subject completions with sustainability-related content are sometimes used as a proxy indicator, the Faculty continues to view this as a limited and potentially misleading measure. Sustainability capability at ABP is increasingly developed through integrated curricula, studio-based learning, project work, and practice-oriented engagement, where sustainability is embedded in learning outcomes, assessment criteria, and decision-making processes rather than delivered as discrete content that can be easily counted.
@@ -1947,36 +1911,36 @@
 The Faculty acknowledges that these outcomes are not yet systematically captured through a formal reporting framework. Over time, ABP intends to develop more meaningful indicators of graduate sustainability capability, potentially combining curriculum mapping, assessment alignment, graduate destination insights, and qualitative exemplars of student work. This will support more robust reporting in future Sustainability Plan refresh cycles, while ensuring that measurement aligns with the complexity and integrated nature of sustainability education within the built environment disciplines.</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr"/>
-      <c r="H13" s="14" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr"/>
+      <c r="H13" s="12" t="inlineStr"/>
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="160" customHeight="1">
-      <c r="B14" s="12" t="inlineStr">
+    <row r="14" ht="409" customHeight="1">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>5b(i)</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Please update data on sustainability-, climate- or environment-focused research institutes, and provide a case study of their key research impacts in 2025.</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>The Faculty continues to be a national and international leader in sustainability research across the built environment, supported by a diverse ecosystem of specialist research hubs, laboratories, and collaborative initiatives. Together, these centres span disciplinary and interdisciplinary research, linking fundamental inquiry with applied outcomes that inform practice, policy, and industry transformation.
 Sustainability-, climate-, and environment-focused research institutes and hubs within the Faculty include:
@@ -1990,7 +1954,7 @@
 These research hubs collectively contribute to advancing knowledge across design, planning, construction, and policy, while also creating pathways for translation into real-world impact.</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>A flagship example of the Faculty’s research impact in 2025 is Beyond EPiC, a research-led spin-off emerging from long-standing work within the Faculty on life cycle assessment (LCA), embodied carbon, and environmental performance of the built environment.
 Beyond EPiC provides a clear example of how the Faculty’s sustainability research translates into action and impact at scale. Emerging directly from decades of peer-reviewed research at the University of Melbourne, Beyond EPiC develops environmental data, digital tools, and applied insights that help architects, engineers, planners, developers, and policymakers make evidence-based decisions across the built environment.
@@ -2001,39 +1965,39 @@
 As such, Beyond EPiC exemplifies the Faculty’s model of sustainability research impact: scientifically rigorous, trusted by government, used at scale, and capable of shaping policy, professional practice, and environmental outcomes simultaneously.</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>www.beyondepic.io</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>TR2(a), TR2(d)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="160" customHeight="1">
-      <c r="B15" s="12" t="inlineStr">
+    <row r="15" ht="409" customHeight="1">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>5c(ii)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Researchers make considered decisions on the sustainability impact of their research practices and activities</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Are there any efforts within the faculty to make research practices more sustainable? If so, please describe these activities</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>The Faculty has taken deliberate and strategic steps in 2025 to strengthen how sustainability considerations shape research practices and activities. This has focused on making sustainability explicit, visible, and rewarded within the Faculty’s research culture, while building the foundations for longer-term embedding across disciplines.
 A major development has been the introduction of formal recognition and incentive mechanisms that foreground sustainability in research excellence. The ABP Sustainability Award, embedded within the Faculty’s Engagement, Culture, Innovation, and Impact awards program, recognises academic and professional staff who demonstrate leadership in integrating sustainability into research practices. By celebrating approaches such as life cycle thinking, low-carbon methodologies, resource efficiency, and collaborative research models, the award signals that sustainability is a core dimension of research quality and impact within ABP.
@@ -2042,36 +2006,36 @@
 Together, these initiatives reflect a maturing research culture in which sustainability is increasingly normalised, recognised, and actively shaped through incentives, methods, and shared expectations. While this work will continue to evolve and scale, 2025 represents a clear step change in positioning sustainability as a defining feature of responsible research practice within the Faculty.</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr"/>
-      <c r="H15" s="14" t="inlineStr"/>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr"/>
+      <c r="H15" s="12" t="inlineStr"/>
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>TR3(a), TR3(b)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="160" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+    <row r="16" ht="409" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Please provide a case study on activities in the faculty (related to education, research or partnerships) which operate at the nexus between Indigenous knowledges and the western concept of 'sustainability'.</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>In 2025, the Faculty has continued to deepen its engagement with sustainability through Indigenous-led and co-created learning, research, and partnerships, strengthening understanding of sustainability as a Country-centred, relational, and long-term responsibility rather than a purely technical or extractive concept.
 A major development is the award of an ARC Linkage Project: Co-designing Housing for First Nations Prosperity, which will commence in 2026. This project represents a significant example of sustainability research grounded in First Nations leadership, knowledge, and lived experience, operating at the intersection of architecture, housing policy, economics, and Indigenous wellbeing.
@@ -2082,9 +2046,9 @@
 Collectively, these initiatives demonstrate that the Faculty’s approach to sustainability is increasingly shaped through Indigenous-led knowledge systems, reciprocal learning, and co-creation, contributing to more just, culturally grounded, and enduring sustainability outcomes across education, research, and practice.</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr"/>
-      <c r="H16" s="14" t="inlineStr"/>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr"/>
+      <c r="H16" s="12" t="inlineStr"/>
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
@@ -2107,10 +2071,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="B1" t="inlineStr">
         <is>
           <t>(not used – no target status rating in 2026)</t>
@@ -2132,7 +2103,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
           <t>Please select from dropdown</t>
@@ -2154,7 +2125,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -2171,7 +2142,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -2188,35 +2159,35 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>Not required</t>

--- a/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
@@ -633,7 +633,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
@@ -31,7 +31,7 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00002060"/>
+      <color rgb="00FFFFFF"/>
       <sz val="22"/>
     </font>
     <font>
@@ -110,7 +110,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00000F46"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,9 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -297,6 +305,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -608,24 +706,61 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -633,7 +768,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Thursday 24 December 2026 (Christmas shutdown). Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>
@@ -644,7 +779,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>ABP – Faculty of Architecture, Building and Planning</t>
         </is>
@@ -652,191 +787,191 @@
     </row>
     <row r="12"/>
     <row r="13" ht="27" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="81" customHeight="1">
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="320" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+    <row r="16" ht="352" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples from 2026 of how your faculty has embedded sustainability in teaching and learning. This could include innovative approaches (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment or learning resources) and sustainability-focused experiential or co-curricular learning (e.g. industry or community projects, fieldwork, internships, student challenges). Include links and approximate student participation where known.
-This question also covers indicator EE1(c). Melbourne Plus and the Wattle Fellowship will be collected separately – no need to report these.</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples from 2026 of how your faculty has embedded sustainability in teaching and learning. This could include innovative approaches (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment or learning resources) and sustainability-focused experiential or co-curricular learning (e.g. industry or community projects, fieldwork, internships, student challenges). Include links and approximate student participation where known.
+This question also covers indicator EE1(c). Please note that this indicator will be addressed at the joint Associate Deans Sustainability and Associate Deans Teaching and Learning session on 23 November 2026. Please feel free to summarise what your faculty presented at this session - further information is welcome but not required.
+In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>4a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>The Faculty has continued to make substantial and discipline-wide progress in embedding sustainability into the curriculum in ways that extend well beyond baseline requirements, ensuring that students critically engage with both the beneficial and harmful impacts of the built environment on environmental and human systems.
 A central mechanism for this work in 2025 has been the forward planning and strategic renewal of all Master’s programs across the Faculty, led by Professor Dan Hill under the Designing Futures strategy. This process goes beyond incremental subject updates and instead focuses on holistic program-level reform, explicitly positioning sustainability as a core organising principle rather than an add-on topic.
@@ -850,106 +985,59 @@
 Together, these initiatives demonstrate a deliberate and sustained commitment to embedding sustainability deeply and coherently across the curriculum, ensuring that graduates across all disciplines develop a critical understanding of the environmental and human systems they shape through professional practice.</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="188" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>EE1(b)</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Exceptional education</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>Has your faculty piloted or trialled any approach in 2026 to understand or build students' confidence and capability to act on sustainability (sustainability self-efficacy)? If yes, briefly describe the approach, participating cohort, what was learned and next steps. If not, please respond 'none in 2026' – this is a new indicator and a nil response is useful.
-We are aware of the Sustainability Strengths Compass Living Lab project (CLLAP) and will collect it separately.</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>N/A – new indicator</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="14" t="n"/>
-      <c r="N17" s="14" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
-      <c r="Q17" s="14" t="n"/>
-    </row>
-    <row r="18" ht="303" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="270" customHeight="1">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
-We will collect Campus Living Lab Accelerator Program (CLLAP) projects separately from CI&amp;S – please include other examples only.</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
+Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
+In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners, and share them with operational teams to identify further collaboration.</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>Across 2025, the Faculty of Architecture, Building and Planning has significantly strengthened and formalised its Living Labs approach, building on progress reported at mid-year and embedding sustainability experimentation as a core mode of practice across teaching, research, and operations.
 A major development in the second half of 2025 was the establishment of the ABP Sustainability Grant. This new internal funding scheme provides up to $10,000 annually to catalyse staff-led, cross-disciplinary sustainability initiatives that operate as Living Labs within the Faculty. The scheme supports projects that use real faculty contexts—spaces, systems, practices, and communities—as testbeds for sustainability innovation, with strong encouragement for student involvement, particularly graduate researchers.
@@ -963,59 +1051,59 @@
 Together with the newly established ABP Sustainability Grant, the Interactive Campus Material and Carbon Atlas illustrates how the Faculty is operationalising Living Labs across scales—from grassroots initiatives to faculty-wide decision-support infrastructure.</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14" t="n"/>
-      <c r="N18" s="14" t="n"/>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="14" t="n"/>
-      <c r="Q18" s="14" t="n"/>
-    </row>
-    <row r="19" ht="286" customHeight="1">
-      <c r="B19" s="10" t="inlineStr">
+      <c r="K17" s="13" t="inlineStr"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="15" t="n"/>
+    </row>
+    <row r="18" ht="270" customHeight="1">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>TR2(a)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
-We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from MRE – publication counts are not required.</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from MRE.</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
+We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from Melbourne Research and Enterprise (MRE) – publication counts are not required.
+In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from Melbourne Research and Enterprise (MRE).</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>The Faculty continues to be a national and international leader in sustainability research across the built environment, supported by a diverse ecosystem of specialist research hubs, laboratories, and collaborative initiatives. Together, these centres span disciplinary and interdisciplinary research, linking fundamental inquiry with applied outcomes that inform practice, policy, and industry transformation.
 Sustainability-, climate-, and environment-focused research institutes and hubs within the Faculty include:
@@ -1036,63 +1124,63 @@
 As such, Beyond EPiC exemplifies the Faculty’s model of sustainability research impact: scientifically rigorous, trusted by government, used at scale, and capable of shaping policy, professional practice, and environmental outcomes simultaneously.</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr">
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>www.beyondepic.io</t>
         </is>
       </c>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="14" t="n"/>
-      <c r="N19" s="14" t="n"/>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="14" t="n"/>
-      <c r="Q19" s="14" t="n"/>
-    </row>
-    <row r="20" ht="270" customHeight="1">
-      <c r="B20" s="10" t="inlineStr">
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="237" customHeight="1">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>TR2(d)</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
-We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
+We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.
+In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>The Faculty continues to be a national and international leader in sustainability research across the built environment, supported by a diverse ecosystem of specialist research hubs, laboratories, and collaborative initiatives. Together, these centres span disciplinary and interdisciplinary research, linking fundamental inquiry with applied outcomes that inform practice, policy, and industry transformation.
 Sustainability-, climate-, and environment-focused research institutes and hubs within the Faculty include:
@@ -1113,62 +1201,62 @@
 As such, Beyond EPiC exemplifies the Faculty’s model of sustainability research impact: scientifically rigorous, trusted by government, used at scale, and capable of shaping policy, professional practice, and environmental outcomes simultaneously.</t>
         </is>
       </c>
-      <c r="K20" s="12" t="inlineStr">
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>www.beyondepic.io</t>
         </is>
       </c>
-      <c r="L20" s="14" t="n"/>
-      <c r="M20" s="14" t="n"/>
-      <c r="N20" s="14" t="n"/>
-      <c r="O20" s="14" t="n"/>
-      <c r="P20" s="14" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-    </row>
-    <row r="21" ht="220" customHeight="1">
-      <c r="B21" s="10" t="inlineStr">
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="15" t="n"/>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="15" t="n"/>
+      <c r="Q19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="188" customHeight="1">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.
+In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>5c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>The Faculty has taken deliberate and strategic steps in 2025 to strengthen how sustainability considerations shape research practices and activities. This has focused on making sustainability explicit, visible, and rewarded within the Faculty’s research culture, while building the foundations for longer-term embedding across disciplines.
 A major development has been the introduction of formal recognition and incentive mechanisms that foreground sustainability in research excellence. The ABP Sustainability Award, embedded within the Faculty’s Engagement, Culture, Innovation, and Impact awards program, recognises academic and professional staff who demonstrate leadership in integrating sustainability into research practices. By celebrating approaches such as life cycle thinking, low-carbon methodologies, resource efficiency, and collaborative research models, the award signals that sustainability is a core dimension of research quality and impact within ABP.
@@ -1177,58 +1265,58 @@
 Together, these initiatives reflect a maturing research culture in which sustainability is increasingly normalised, recognised, and actively shaped through incentives, methods, and shared expectations. While this work will continue to evolve and scale, 2025 represents a clear step change in positioning sustainability as a defining feature of responsible research practice within the Faculty.</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="14" t="n"/>
-      <c r="N21" s="14" t="n"/>
-      <c r="O21" s="14" t="n"/>
-      <c r="P21" s="14" t="n"/>
-      <c r="Q21" s="14" t="n"/>
-    </row>
-    <row r="22" ht="220" customHeight="1">
-      <c r="B22" s="10" t="inlineStr">
+      <c r="K20" s="13" t="inlineStr"/>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="n"/>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="188" customHeight="1">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.
+In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>6a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>In 2025, the Faculty has continued to deepen its engagement with sustainability through Indigenous-led and co-created learning, research, and partnerships, strengthening understanding of sustainability as a Country-centred, relational, and long-term responsibility rather than a purely technical or extractive concept.
 A major development is the award of an ARC Linkage Project: Co-designing Housing for First Nations Prosperity, which will commence in 2026. This project represents a significant example of sustainability research grounded in First Nations leadership, knowledge, and lived experience, operating at the intersection of architecture, housing policy, economics, and Indigenous wellbeing.
@@ -1239,59 +1327,59 @@
 Collectively, these initiatives demonstrate that the Faculty’s approach to sustainability is increasingly shaped through Indigenous-led knowledge systems, reciprocal learning, and co-creation, contributing to more just, culturally grounded, and enduring sustainability outcomes across education, research, and practice.</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="14" t="n"/>
-      <c r="N22" s="14" t="n"/>
-      <c r="O22" s="14" t="n"/>
-      <c r="P22" s="14" t="n"/>
-      <c r="Q22" s="14" t="n"/>
-    </row>
-    <row r="23" ht="254" customHeight="1">
-      <c r="B23" s="10" t="inlineStr">
+      <c r="K21" s="13" t="inlineStr"/>
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="15" t="n"/>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="15" t="n"/>
+      <c r="Q21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="220" customHeight="1">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
-Please note we will approach living labs funded through the Campus Living Lab Accelerator Program (CLLAP) separately.</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
+Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
+In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners.</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>Across 2025, the Faculty of Architecture, Building and Planning has significantly strengthened and formalised its Living Labs approach, building on progress reported at mid-year and embedding sustainability experimentation as a core mode of practice across teaching, research, and operations.
 A major development in the second half of 2025 was the establishment of the ABP Sustainability Grant. This new internal funding scheme provides up to $10,000 annually to catalyse staff-led, cross-disciplinary sustainability initiatives that operate as Living Labs within the Faculty. The scheme supports projects that use real faculty contexts—spaces, systems, practices, and communities—as testbeds for sustainability innovation, with strong encouragement for student involvement, particularly graduate researchers.
@@ -1305,58 +1393,58 @@
 Together with the newly established ABP Sustainability Grant, the Interactive Campus Material and Carbon Atlas illustrates how the Faculty is operationalising Living Labs across scales—from grassroots initiatives to faculty-wide decision-support infrastructure.</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr"/>
-      <c r="L23" s="14" t="n"/>
-      <c r="M23" s="14" t="n"/>
-      <c r="N23" s="14" t="n"/>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="n"/>
-      <c r="Q23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="188" customHeight="1">
-      <c r="B24" s="10" t="inlineStr">
+      <c r="K22" s="13" t="inlineStr"/>
+      <c r="L22" s="15" t="n"/>
+      <c r="M22" s="15" t="n"/>
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="154" customHeight="1">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.
+In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I23" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>In 2025, ABP continued to support sustainability-focused communities of practice that enable staff to learn from one another and embed sustainability across formal, non-formal, and informal learning contexts. These communities operate through a combination of structured forums, shared initiatives, and recognition mechanisms that make sustainability practice visible, valued, and transferable across the Faculty.
 Core to this ecosystem is the Faculty’s Climate Action Group, which continues to provide a cross-disciplinary forum for peer learning, curriculum coordination, and shared reflection on sustainability pedagogy and practice. The Group has supported sustained collaboration across academic and professional staff and has played a key role in aligning Faculty initiatives with University sustainability priorities.
@@ -1368,15 +1456,15 @@
 In this way, the Sustainability Award complements more formal communities of practice by creating a visible, Faculty-wide platform for knowledge sharing, inspiration, and peer learning. It supports sustainability not only as a technical or curricular concern, but as a shared professional and cultural endeavour.</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr"/>
-      <c r="L24" s="14" t="n"/>
-      <c r="M24" s="14" t="n"/>
-      <c r="N24" s="14" t="n"/>
-      <c r="O24" s="14" t="n"/>
-      <c r="P24" s="14" t="n"/>
-      <c r="Q24" s="14" t="n"/>
-    </row>
-    <row r="25"/>
+      <c r="K23" s="13" t="inlineStr"/>
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="15" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="15" t="n"/>
+      <c r="Q23" s="15" t="n"/>
+    </row>
+    <row r="24"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
@@ -1386,21 +1474,22 @@
     <mergeCell ref="B4:C8"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="P16:P24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+    <dataValidation sqref="P16:P23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B12"/>
-    <hyperlink ref="H18" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H17" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H18" location="'3. SR25 responses'!B14"/>
     <hyperlink ref="H19" location="'3. SR25 responses'!B14"/>
-    <hyperlink ref="H20" location="'3. SR25 responses'!B14"/>
-    <hyperlink ref="H21" location="'3. SR25 responses'!B15"/>
-    <hyperlink ref="H22" location="'3. SR25 responses'!B16"/>
-    <hyperlink ref="H23" location="'3. SR25 responses'!B8"/>
-    <hyperlink ref="H24" location="'3. SR25 responses'!B10"/>
+    <hyperlink ref="H20" location="'3. SR25 responses'!B15"/>
+    <hyperlink ref="H21" location="'3. SR25 responses'!B16"/>
+    <hyperlink ref="H22" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H23" location="'3. SR25 responses'!B10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1410,7 +1499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1423,104 +1512,148 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Thursday 24 December 2026 (Christmas shutdown) (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1528,6 +1661,7 @@
     <mergeCell ref="C5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1537,7 +1671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1549,101 +1683,146 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Your SR25 responses – Faculty of Architecture, Building and Planning</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>ABP</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="409" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>1a(i)</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Comment on progress to reduce air travel emissions in the faculty</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Faculty-level air travel data for 2025 indicates that the Faculty of Architecture, Building and Planning (ABP) has continued to reduce its contribution to University-wide air travel emissions, supporting progress toward the University’s carbon neutrality target.
 According to the 2025 Flights Dashboard, ABP recorded 375 tCO₂-e from air travel in 2025, representing approximately 2% of total University air travel emissions. This places ABP among the lowest-emitting faculties in absolute terms, despite the Faculty’s strong international research and engagement profile.
@@ -1659,37 +1838,37 @@
 While international travel remains a significant and sometimes necessary component of ABP’s research and engagement activities, the 2025 data indicates that the Faculty has achieved meaningful and sustained reductions in air travel emissions relative to historic levels. Further opportunities for reduction are being explored through internal discussions on travel justification, approval processes, and the strategic use of low-carbon alternatives, with a view to consolidating and extending these gains into 2026 and beyond.</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/links/SI8xYFLga4?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;pbi_source=linkShare&amp;bookmarkGuid=499326eb-68f1-43e0-a3e6-0f252ee44ccb</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="409" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Please provide a case study of a living lab which operates within the faculty/portfolio, including a description of its activities and impact. 
 Please note we will approach living labs funded through the Campus Living Lab Accelerator program (CLLAP) separately report on their activities.</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>Across 2025, the Faculty of Architecture, Building and Planning has significantly strengthened and formalised its Living Labs approach, building on progress reported at mid-year and embedding sustainability experimentation as a core mode of practice across teaching, research, and operations.
 A major development in the second half of 2025 was the establishment of the ABP Sustainability Grant. This new internal funding scheme provides up to $10,000 annually to catalyse staff-led, cross-disciplinary sustainability initiatives that operate as Living Labs within the Faculty. The scheme supports projects that use real faculty contexts—spaces, systems, practices, and communities—as testbeds for sustainability innovation, with strong encouragement for student involvement, particularly graduate researchers.
@@ -1698,7 +1877,7 @@
 Collectively, these initiatives demonstrate that ABP is not only contributing to the University’s Living Labs agenda, but actively curating, resourcing, and governing Living Labs as a sustained and scalable approach to sustainability action.</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>A flagship example of the Faculty’s Living Labs approach in 2025 is the Interactive Campus Material and Carbon Atlas, which reached completion during the year. Funded through the Learning and Teaching Initiative (LTI), the project brought together academic staff, professional colleagues, and students to map and analyse the material stock and embodied carbon of selected University buildings.
 The Atlas has been developed as an interactive digital tool that enables users to explore building-level data, including construction materials, embodied carbon intensities, and potential opportunities for material reuse and circularity. Importantly, the project moves beyond retrospective analysis: the underlying framework enables forward projection of material requirements and carbon implications under different development and renewal scenarios.
@@ -1707,35 +1886,35 @@
 Together with the newly established ABP Sustainability Grant, the Interactive Campus Material and Carbon Atlas illustrates how the Faculty is operationalising Living Labs across scales—from grassroots initiatives to faculty-wide decision-support infrastructure.</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>TR1(a), EN1(b)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="409" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>3a(i)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Please update data on sustainability-focused staff in the faculty/portfolio provided in the previous reporting period (additional staff/those who have left the University) (see Columns G [2024] and J [mid-2025])</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>In 2025, ABP continued to strengthen how sustainability is embedded across formal, non-formal, and informal learning and practice through distributed leadership and coordinated collaboration. Strategic oversight is provided through the Assistant Dean (Sustainability) role, alongside active cross-disciplinary networks (including the Climate Action Group) that support curriculum integration, peer learning, and shared resourcing across departments.
 A key step-change in the second half of 2025 was the establishment of the ABP Sustainability Grant, which has also functioned as a practical mechanism for identifying, mobilising, and connecting sustainability-focused staff across the Faculty. The scheme requires project teams to include both academic and professional staff, with strong encouragement for student involvement. This requirement has actively enabled collaboration between staff groups that do not typically co-lead initiatives together, supporting mutual learning and the transfer of sustainability knowledge into operational and teaching contexts.
@@ -1743,7 +1922,7 @@
 Regardless of the final funding outcomes, the Faculty is committed to supporting high-quality proposals and ensuring that strong ideas emerging through the scheme are enabled to progress—either through the grant itself or through alternative pathways—so that sustainability leadership and learning continues to be shared and scaled across ABP.</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>As supporting evidence of increased sustainability-focused participation and cross-role collaboration in 2025, the Faculty established the ABP Sustainability Grant, which requires teams to include at least one academic and one professional staff member and encourages student participation. The inaugural round drew multiple applications across diverse roles and disciplines, including proposals focused on:
 &gt; establishing a circular timber pathway through salvage, low-energy processing, and reuse integrated with teaching and workshop operations; and
@@ -1751,31 +1930,31 @@
 These proposals demonstrate both the breadth of sustainability-focused staff across ABP and the Faculty’s active approach to enabling staff to support and learn from each other in embedding sustainability into practice and learning.</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="12" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="409" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>3a(ii)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Please list sustainability-focused knowledge sharing activities or communities of practice active in the faculty/portfolio in 2025, and provide a short case study of one of these.</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>In 2025, ABP continued to support sustainability-focused communities of practice that enable staff to learn from one another and embed sustainability across formal, non-formal, and informal learning contexts. These communities operate through a combination of structured forums, shared initiatives, and recognition mechanisms that make sustainability practice visible, valued, and transferable across the Faculty.
 Core to this ecosystem is the Faculty’s Climate Action Group, which continues to provide a cross-disciplinary forum for peer learning, curriculum coordination, and shared reflection on sustainability pedagogy and practice. The Group has supported sustained collaboration across academic and professional staff and has played a key role in aligning Faculty initiatives with University sustainability priorities.
@@ -1783,7 +1962,7 @@
 Complementing these collaborative forums, the Faculty introduced the ABP Sustainability Award as a mechanism for amplifying and connecting sustainability practice across teaching, research, operations, and Faculty culture. Together, these initiatives demonstrate a mature and multi-layered approach to building sustainability-focused communities of practice—combining regular peer engagement, high-impact knowledge exchange, and recognition of exemplary work to support ongoing learning and leadership in sustainability.</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>Introduced in 2025, the ABP Sustainability Award functions as a Faculty-wide community-of-practice mechanism by recognising, showcasing, and disseminating exemplary sustainability initiatives led by academic and professional staff. Rather than operating solely as an individual award, the scheme is designed to surface transferable practices and create shared reference points for sustainability leadership across ABP.
 The Award recognises excellence across a broad set of criteria, including innovation and leadership, collaboration and engagement, measurable environmental outcomes, integration of sustainability into teaching and learning, influence on policy and professional practice, and contributions to a culture of sustainability within the Faculty. Eligible initiatives span teaching, research, operations, and cultural change, reflecting the diverse ways sustainability is embedded across ABP.
@@ -1791,36 +1970,36 @@
 In this way, the Sustainability Award complements more formal communities of practice by creating a visible, Faculty-wide platform for knowledge sharing, inspiration, and peer learning. It supports sustainability not only as a technical or curricular concern, but as a shared professional and cultural endeavour.</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="409" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>3d(ii)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Have any staff participated in sustainability-focused professional development in 2025? If yes, what kinds of activities have staff participated in and how are these learnings being applied in the faculty/portfolio?
 Please note, there is no need to include data on participation in Green Impact ('Green teams'), as this is reported on centrally.</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>In 2025, ABP supported the development of staff sustainability capability through a combination of non-formal, practice-based learning and peer-led knowledge exchange. While participation in centrally delivered, formal professional development was limited due to broader institutional transitions, the Faculty remained actively engaged in alternative learning pathways that supported both general and role-specific sustainability skills.
 As reported at mid-year, several established executive and professional education offerings—including the Embodied Carbon Masterclass previously delivered in partnership with MSPACE—were paused in 2025 as delivery models were reviewed. In response, the Faculty placed greater emphasis on applied, embedded learning opportunities linked directly to teaching, research, and professional practice.
@@ -1831,32 +2010,32 @@
 These activities enabled staff to develop and apply sustainability skills directly relevant to their roles, while also fostering peer learning across disciplines and professional functions. While formal professional development participation remained stable in 2025, these applied learning initiatives ensured continued capability building during a period of transition, with significant expansion anticipated through the Faculty’s refreshed executive and professional education model from 2027.</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr"/>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="12" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr"/>
     </row>
     <row r="12" ht="409" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>4a(ii)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Please describe any efforts within your faculty to embed sustainability in the curriculum in line with this target.</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>The Faculty has continued to make substantial and discipline-wide progress in embedding sustainability into the curriculum in ways that extend well beyond baseline requirements, ensuring that students critically engage with both the beneficial and harmful impacts of the built environment on environmental and human systems.
 A central mechanism for this work in 2025 has been the forward planning and strategic renewal of all Master’s programs across the Faculty, led by Professor Dan Hill under the Designing Futures strategy. This process goes beyond incremental subject updates and instead focuses on holistic program-level reform, explicitly positioning sustainability as a core organising principle rather than an add-on topic.
@@ -1870,36 +2049,36 @@
 Together, these initiatives demonstrate a deliberate and sustained commitment to embedding sustainability deeply and coherently across the curriculum, ensuring that graduates across all disciplines develop a critical understanding of the environmental and human systems they shape through professional practice.</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr"/>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="409" customHeight="1">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>4b(i)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead and succeed in the careers, communities and industries of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Is there any way to measure graduate outcomes related to sustainability in your faculty? If so, please describe.</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>The Faculty recognises the importance of understanding how graduates develop the capabilities required to shape, lead and succeed in sustainable societies. At present, however, there is no single quantitative metric that adequately captures graduate sustainability capability across the breadth and depth of the Faculty’s programs.
 While subject completions with sustainability-related content are sometimes used as a proxy indicator, the Faculty continues to view this as a limited and potentially misleading measure. Sustainability capability at ABP is increasingly developed through integrated curricula, studio-based learning, project work, and practice-oriented engagement, where sustainability is embedded in learning outcomes, assessment criteria, and decision-making processes rather than delivered as discrete content that can be easily counted.
@@ -1911,36 +2090,36 @@
 The Faculty acknowledges that these outcomes are not yet systematically captured through a formal reporting framework. Over time, ABP intends to develop more meaningful indicators of graduate sustainability capability, potentially combining curriculum mapping, assessment alignment, graduate destination insights, and qualitative exemplars of student work. This will support more robust reporting in future Sustainability Plan refresh cycles, while ensuring that measurement aligns with the complexity and integrated nature of sustainability education within the built environment disciplines.</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr"/>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr"/>
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="409" customHeight="1">
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>5b(i)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Please update data on sustainability-, climate- or environment-focused research institutes, and provide a case study of their key research impacts in 2025.</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>The Faculty continues to be a national and international leader in sustainability research across the built environment, supported by a diverse ecosystem of specialist research hubs, laboratories, and collaborative initiatives. Together, these centres span disciplinary and interdisciplinary research, linking fundamental inquiry with applied outcomes that inform practice, policy, and industry transformation.
 Sustainability-, climate-, and environment-focused research institutes and hubs within the Faculty include:
@@ -1954,7 +2133,7 @@
 These research hubs collectively contribute to advancing knowledge across design, planning, construction, and policy, while also creating pathways for translation into real-world impact.</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>A flagship example of the Faculty’s research impact in 2025 is Beyond EPiC, a research-led spin-off emerging from long-standing work within the Faculty on life cycle assessment (LCA), embodied carbon, and environmental performance of the built environment.
 Beyond EPiC provides a clear example of how the Faculty’s sustainability research translates into action and impact at scale. Emerging directly from decades of peer-reviewed research at the University of Melbourne, Beyond EPiC develops environmental data, digital tools, and applied insights that help architects, engineers, planners, developers, and policymakers make evidence-based decisions across the built environment.
@@ -1965,39 +2144,39 @@
 As such, Beyond EPiC exemplifies the Faculty’s model of sustainability research impact: scientifically rigorous, trusted by government, used at scale, and capable of shaping policy, professional practice, and environmental outcomes simultaneously.</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>www.beyondepic.io</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>TR2(a), TR2(d)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="409" customHeight="1">
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>5c(ii)</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Researchers make considered decisions on the sustainability impact of their research practices and activities</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Are there any efforts within the faculty to make research practices more sustainable? If so, please describe these activities</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>The Faculty has taken deliberate and strategic steps in 2025 to strengthen how sustainability considerations shape research practices and activities. This has focused on making sustainability explicit, visible, and rewarded within the Faculty’s research culture, while building the foundations for longer-term embedding across disciplines.
 A major development has been the introduction of formal recognition and incentive mechanisms that foreground sustainability in research excellence. The ABP Sustainability Award, embedded within the Faculty’s Engagement, Culture, Innovation, and Impact awards program, recognises academic and professional staff who demonstrate leadership in integrating sustainability into research practices. By celebrating approaches such as life cycle thinking, low-carbon methodologies, resource efficiency, and collaborative research models, the award signals that sustainability is a core dimension of research quality and impact within ABP.
@@ -2006,36 +2185,36 @@
 Together, these initiatives reflect a maturing research culture in which sustainability is increasingly normalised, recognised, and actively shaped through incentives, methods, and shared expectations. While this work will continue to evolve and scale, 2025 represents a clear step change in positioning sustainability as a defining feature of responsible research practice within the Faculty.</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>TR3(a), TR3(b)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="409" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Please provide a case study on activities in the faculty (related to education, research or partnerships) which operate at the nexus between Indigenous knowledges and the western concept of 'sustainability'.</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>In 2025, the Faculty has continued to deepen its engagement with sustainability through Indigenous-led and co-created learning, research, and partnerships, strengthening understanding of sustainability as a Country-centred, relational, and long-term responsibility rather than a purely technical or extractive concept.
 A major development is the award of an ARC Linkage Project: Co-designing Housing for First Nations Prosperity, which will commence in 2026. This project represents a significant example of sustainability research grounded in First Nations leadership, knowledge, and lived experience, operating at the intersection of architecture, housing policy, economics, and Indigenous wellbeing.
@@ -2046,9 +2225,9 @@
 Collectively, these initiatives demonstrate that the Faculty’s approach to sustainability is increasingly shaped through Indigenous-led knowledge systems, reciprocal learning, and co-creation, contributing to more just, culturally grounded, and enduring sustainability outcomes across education, research, and practice.</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr"/>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
@@ -2062,6 +2241,7 @@
     <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/ABP - SR26 sustainability reporting request.xlsx
@@ -703,9 +703,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -764,7 +764,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -803,7 +804,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -871,17 +872,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -913,17 +904,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
@@ -990,8 +971,6 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="270" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
@@ -1056,8 +1035,6 @@
       <c r="M17" s="15" t="n"/>
       <c r="N17" s="15" t="n"/>
       <c r="O17" s="15" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="15" t="n"/>
     </row>
     <row r="18" ht="270" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
@@ -1133,8 +1110,6 @@
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="15" t="n"/>
     </row>
     <row r="19" ht="237" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
@@ -1210,8 +1185,6 @@
       <c r="M19" s="15" t="n"/>
       <c r="N19" s="15" t="n"/>
       <c r="O19" s="15" t="n"/>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="15" t="n"/>
     </row>
     <row r="20" ht="188" customHeight="1">
       <c r="B20" s="11" t="inlineStr">
@@ -1270,8 +1243,6 @@
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
-      <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="15" t="n"/>
     </row>
     <row r="21" ht="188" customHeight="1">
       <c r="B21" s="11" t="inlineStr">
@@ -1332,8 +1303,6 @@
       <c r="M21" s="15" t="n"/>
       <c r="N21" s="15" t="n"/>
       <c r="O21" s="15" t="n"/>
-      <c r="P21" s="15" t="n"/>
-      <c r="Q21" s="15" t="n"/>
     </row>
     <row r="22" ht="220" customHeight="1">
       <c r="B22" s="11" t="inlineStr">
@@ -1398,8 +1367,6 @@
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
-      <c r="P22" s="15" t="n"/>
-      <c r="Q22" s="15" t="n"/>
     </row>
     <row r="23" ht="154" customHeight="1">
       <c r="B23" s="11" t="inlineStr">
@@ -1424,13 +1391,13 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.
+          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a sustainability outcome.
 In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
+          <t>We will report on internal engagement and partnerships contributing to sustainability outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -1461,23 +1428,16 @@
       <c r="M23" s="15" t="n"/>
       <c r="N23" s="15" t="n"/>
       <c r="O23" s="15" t="n"/>
-      <c r="P23" s="15" t="n"/>
-      <c r="Q23" s="15" t="n"/>
     </row>
     <row r="24"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P16:P23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B12"/>
     <hyperlink ref="H17" location="'3. SR25 responses'!B8"/>
